--- a/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Easthill_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Easthill_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>23.75</v>
       </c>
       <c r="E4" t="n">
-        <v>47.5</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="5">
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>10.25</v>
       </c>
       <c r="E7" t="n">
-        <v>30.75</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="8">
@@ -630,6 +630,27 @@
       </c>
       <c r="E10" t="n">
         <v>11.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>004051</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Natalie's - Grapefruit</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13.25</v>
       </c>
     </row>
   </sheetData>
